--- a/17 18 20/Excel/4.Advanced Tools & Automation/Basic Excel Formulas.xlsx
+++ b/17 18 20/Excel/4.Advanced Tools & Automation/Basic Excel Formulas.xlsx
@@ -4,21 +4,22 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" firstSheet="2" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Basic Mathematical Formulas" sheetId="2" r:id="rId2"/>
     <sheet name="Statistical Formulas" sheetId="3" r:id="rId3"/>
     <sheet name="Date &amp; Time Functions" sheetId="4" r:id="rId4"/>
-    <sheet name="COUNTfUNCTIONS" sheetId="5" r:id="rId5"/>
-    <sheet name="Sheet5" sheetId="6" r:id="rId6"/>
-    <sheet name="Sheet3" sheetId="8" r:id="rId7"/>
-    <sheet name="Sheet2" sheetId="7" r:id="rId8"/>
+    <sheet name="CountFunctions" sheetId="5" r:id="rId5"/>
+    <sheet name="CountIF(IFS)" sheetId="7" r:id="rId6"/>
+    <sheet name="SumIF(IFS)" sheetId="6" r:id="rId7"/>
+    <sheet name="Sheet3" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId9"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="5" r:id="rId10"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="131">
   <si>
     <t>1. Basic Mathematical Formulas</t>
   </si>
@@ -408,9 +409,6 @@
       </rPr>
       <t xml:space="preserve"> → Adds all numbers in a range</t>
     </r>
-  </si>
-  <si>
-    <t>🎯 Conditional SUM</t>
   </si>
   <si>
     <r>
@@ -596,6 +594,20 @@
   <si>
     <t>=COUNTIFS(cri_r1,cri1,cri_r2,cir2……………)</t>
   </si>
+  <si>
+    <t>Sum of Sales</t>
+  </si>
+  <si>
+    <t>=SUMIFS
+(Sum_Range,
+Cri_Range_01,Cri_01,
+Cri_Range_02,Cri_02…
+……………….)</t>
+  </si>
+  <si>
+    <t>=SUMIF
+(Criteria_Range,Criteria,Sum_Range)</t>
+  </si>
 </sst>
 </file>
 
@@ -604,9 +616,9 @@
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="[$-10409]h\.mm\.ss\ AM/PM;@"/>
-    <numFmt numFmtId="167" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -676,8 +688,36 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -700,6 +740,11 @@
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
   </fills>
@@ -745,11 +790,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -808,10 +854,33 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -830,7 +899,40 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Author" refreshedDate="46206.497360763889" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="32">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:C33" sheet="Sheet2"/>
+    <worksheetSource ref="A1:C33" sheet="CountIF(IFS)" r:id="rId2"/>
+  </cacheSource>
+  <cacheFields count="3">
+    <cacheField name="Region" numFmtId="0">
+      <sharedItems count="4">
+        <s v="East"/>
+        <s v="North"/>
+        <s v="South"/>
+        <s v="West"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Dept" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Sales"/>
+        <s v="IT"/>
+        <s v="HR"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Sales" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="12" maxValue="100"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Author" refreshedDate="46210.448216203702" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="32">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:C33" sheet="SumIF(IFS)"/>
   </cacheSource>
   <cacheFields count="3">
     <cacheField name="Region" numFmtId="0">
@@ -1025,8 +1127,173 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="32">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="21"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="51"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="60"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="41"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="69"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="76"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="100"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="78"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="56"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="12"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="22"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="60"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="49"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="30"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="82"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="31"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="23"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="44"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="51"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="80"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="40"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="52"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="56"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="74"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="42"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="84"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="48"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="33"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="61"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="58"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="E1:G18" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
@@ -1117,6 +1384,119 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="E1:G18" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
+      <items count="3">
+        <item x="2"/>
+        <item x="1"/>
+        <item x="0"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0" insertBlankRow="1" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="0"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="17">
+    <i>
+      <x/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i t="blank">
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i t="blank">
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i t="blank">
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i t="blank">
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Sales" fld="2" baseField="1" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" fillDownLabelsDefault="1" hideValuesRow="1"/>
     </ext>
   </extLst>
 </pivotTableDefinition>
@@ -1537,7 +1917,7 @@
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:1">
@@ -1547,12 +1927,12 @@
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1786,13 +2166,13 @@
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H1">
         <f>SUM(D2:D10)</f>
@@ -1803,20 +2183,20 @@
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D2">
         <v>1000</v>
       </c>
       <c r="G2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H2">
         <f>AVERAGE(D2:D10)</f>
         <v>157.22222222222223</v>
       </c>
       <c r="I2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1825,13 +2205,13 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D3">
         <v>52</v>
       </c>
       <c r="G3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H3">
         <f>MAX(D2:D10)</f>
@@ -1844,13 +2224,13 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D4">
         <v>76</v>
       </c>
       <c r="G4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H4">
         <f>MIN(D2:D10)</f>
@@ -1863,13 +2243,13 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D5">
         <v>91</v>
       </c>
       <c r="G5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H5">
         <f>COUNTA(D2:D10)</f>
@@ -1882,13 +2262,13 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D6">
         <v>19</v>
       </c>
       <c r="G6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H6">
         <f>COUNTA(C2:C10)</f>
@@ -1901,7 +2281,7 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D7">
         <v>12</v>
@@ -1917,7 +2297,7 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D8">
         <v>45</v>
@@ -1925,7 +2305,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="C9" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D9">
         <v>65</v>
@@ -1933,7 +2313,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="C10" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D10">
         <v>55</v>
@@ -1947,7 +2327,7 @@
     </row>
     <row r="14" spans="1:9" ht="18">
       <c r="C14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1978,7 +2358,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G2">
         <f>MEDIAN(D2:D14)</f>
@@ -1998,7 +2378,7 @@
         <v>2</v>
       </c>
       <c r="F3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G3">
         <f>_xlfn.STDEV.S(D2:D14)</f>
@@ -2022,7 +2402,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G4">
         <f>_xlfn.VAR.S(D2:D14)</f>
@@ -2118,7 +2498,7 @@
         <v>5</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -2130,7 +2510,7 @@
       </c>
       <c r="B3" s="13">
         <f ca="1">TODAY()</f>
-        <v>46206</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -2139,7 +2519,7 @@
       </c>
       <c r="B4" s="14">
         <f ca="1">NOW()</f>
-        <v>46206.508664236113</v>
+        <v>46210.467010995373</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -2172,7 +2552,7 @@
         <v>46206</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -2237,11 +2617,11 @@
     <row r="18" spans="1:6">
       <c r="B18" s="1">
         <f ca="1">HOUR(C18)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" s="14">
         <f ca="1">NOW()</f>
-        <v>46206.508664236113</v>
+        <v>46210.467010995373</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2254,7 +2634,7 @@
       </c>
       <c r="C19" s="14">
         <f ca="1">NOW()</f>
-        <v>46206.508664236113</v>
+        <v>46210.467010995373</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2263,11 +2643,11 @@
       </c>
       <c r="B20" s="1">
         <f ca="1">SECOND(C20)</f>
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20" s="14">
         <f ca="1">NOW()</f>
-        <v>46206.508664236113</v>
+        <v>46210.467010995373</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2355,56 +2735,6 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="73.109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="12" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="18">
-      <c r="A3" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="10"/>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="12" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="12" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="12" t="s">
-        <v>86</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T33"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
@@ -2417,107 +2747,107 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="B1" s="21" t="s">
-        <v>115</v>
-      </c>
       <c r="C1" s="21" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E1" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="F1" s="23" t="s">
-        <v>115</v>
-      </c>
       <c r="G1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I1" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="J1" s="29" t="s">
+        <v>114</v>
+      </c>
+      <c r="P1" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q1" s="27" t="s">
         <v>124</v>
-      </c>
-      <c r="I1" s="29" t="s">
-        <v>114</v>
-      </c>
-      <c r="J1" s="29" t="s">
-        <v>115</v>
-      </c>
-      <c r="P1" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q1" s="27" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="A2" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="22" t="s">
         <v>116</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>117</v>
       </c>
       <c r="C2">
         <v>21</v>
       </c>
       <c r="E2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G2" s="26">
         <v>2</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K2" s="30">
         <f>COUNTIFS($A$2:$A$33,I2,$B$2:$B$33,J2)</f>
         <v>2</v>
       </c>
       <c r="M2" s="28" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q2" s="26">
         <f>COUNTIF($A$2:$A$33,P2)</f>
         <v>8</v>
       </c>
       <c r="T2" s="28" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C3">
         <v>51</v>
       </c>
       <c r="F3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G3" s="26">
         <v>2</v>
       </c>
       <c r="I3" s="24" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K3" s="30">
         <f t="shared" ref="K3:K17" si="0">COUNTIFS($A$2:$A$33,I3,$B$2:$B$33,J3)</f>
         <v>2</v>
       </c>
       <c r="P3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q3" s="26">
         <f t="shared" ref="Q3:Q5" si="1">COUNTIF($A$2:$A$33,P3)</f>
@@ -2526,32 +2856,32 @@
     </row>
     <row r="4" spans="1:20">
       <c r="A4" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C4">
         <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G4" s="26">
         <v>2</v>
       </c>
       <c r="I4" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="J4" t="s">
         <v>116</v>
-      </c>
-      <c r="J4" t="s">
-        <v>117</v>
       </c>
       <c r="K4" s="30">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="P4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q4" s="26">
         <f t="shared" si="1"/>
@@ -2560,10 +2890,10 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C5">
         <v>41</v>
@@ -2574,7 +2904,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q5" s="26">
         <f t="shared" si="1"/>
@@ -2583,35 +2913,35 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C6">
         <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G6" s="26">
         <v>3</v>
       </c>
       <c r="I6" s="24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K6" s="30">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="P6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q6">
         <f>SUM(Q2:Q5)</f>
@@ -2620,25 +2950,25 @@
     </row>
     <row r="7" spans="1:20">
       <c r="A7" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C7">
         <v>76</v>
       </c>
       <c r="F7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G7" s="26">
         <v>2</v>
       </c>
       <c r="I7" s="24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K7" s="30">
         <f t="shared" si="0"/>
@@ -2647,25 +2977,25 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8">
         <v>100</v>
       </c>
       <c r="F8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G8" s="26">
         <v>3</v>
       </c>
       <c r="I8" s="24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K8" s="30">
         <f t="shared" si="0"/>
@@ -2674,10 +3004,10 @@
     </row>
     <row r="9" spans="1:20">
       <c r="A9" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C9">
         <v>78</v>
@@ -2690,28 +3020,28 @@
     </row>
     <row r="10" spans="1:20">
       <c r="A10" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B10" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C10">
         <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G10" s="26">
         <v>3</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K10" s="30">
         <f t="shared" si="0"/>
@@ -2720,25 +3050,25 @@
     </row>
     <row r="11" spans="1:20">
       <c r="A11" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C11">
         <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G11" s="26">
         <v>3</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K11" s="30">
         <f t="shared" si="0"/>
@@ -2747,25 +3077,25 @@
     </row>
     <row r="12" spans="1:20">
       <c r="A12" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C12">
         <v>22</v>
       </c>
       <c r="F12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G12" s="26">
         <v>3</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K12" s="30">
         <f t="shared" si="0"/>
@@ -2774,10 +3104,10 @@
     </row>
     <row r="13" spans="1:20">
       <c r="A13" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C13">
         <v>60</v>
@@ -2790,28 +3120,28 @@
     </row>
     <row r="14" spans="1:20">
       <c r="A14" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="22" t="s">
         <v>116</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>117</v>
       </c>
       <c r="C14">
         <v>49</v>
       </c>
       <c r="E14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G14" s="26">
         <v>3</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K14" s="30">
         <f t="shared" si="0"/>
@@ -2820,25 +3150,25 @@
     </row>
     <row r="15" spans="1:20">
       <c r="A15" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C15">
         <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G15" s="26">
         <v>3</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K15" s="30">
         <f t="shared" si="0"/>
@@ -2847,25 +3177,25 @@
     </row>
     <row r="16" spans="1:20">
       <c r="A16" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B16" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C16">
         <v>82</v>
       </c>
       <c r="F16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G16" s="26">
         <v>3</v>
       </c>
       <c r="I16" s="24" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K16" s="30">
         <f t="shared" si="0"/>
@@ -2874,10 +3204,10 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C17">
         <v>31</v>
@@ -2890,31 +3220,31 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C18">
         <v>23</v>
       </c>
       <c r="E18" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G18" s="26">
         <v>32</v>
       </c>
       <c r="I18" s="25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J18" s="25"/>
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C19">
         <v>44</v>
@@ -2922,10 +3252,10 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C20">
         <v>51</v>
@@ -2933,10 +3263,10 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C21">
         <v>80</v>
@@ -2944,10 +3274,10 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C22">
         <v>40</v>
@@ -2955,10 +3285,10 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C23">
         <v>36</v>
@@ -2966,10 +3296,10 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B24" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C24">
         <v>52</v>
@@ -2977,10 +3307,10 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C25">
         <v>35</v>
@@ -2988,10 +3318,10 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B26" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C26">
         <v>56</v>
@@ -2999,10 +3329,10 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C27">
         <v>74</v>
@@ -3010,10 +3340,10 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C28">
         <v>42</v>
@@ -3021,10 +3351,10 @@
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B29" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C29">
         <v>84</v>
@@ -3032,10 +3362,10 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C30">
         <v>48</v>
@@ -3043,10 +3373,10 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B31" s="22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C31">
         <v>33</v>
@@ -3054,10 +3384,10 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C32">
         <v>61</v>
@@ -3065,10 +3395,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="22" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B33" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C33">
         <v>58</v>
@@ -3077,4 +3407,796 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AA33"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.109375" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.21875" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.77734375" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="3.5546875" customWidth="1"/>
+    <col min="15" max="15" width="2.77734375" customWidth="1"/>
+    <col min="16" max="16" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="1.44140625" customWidth="1"/>
+    <col min="27" max="27" width="74.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" ht="14.4" customHeight="1">
+      <c r="A1" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I1" s="34" t="s">
+        <v>114</v>
+      </c>
+      <c r="J1" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="L1" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q1" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="R1" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="T1" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="U1" s="42"/>
+      <c r="V1" s="42"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="40"/>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
+      <c r="A2" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2" s="26">
+        <v>142</v>
+      </c>
+      <c r="H2" s="26"/>
+      <c r="I2" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="J2" s="26">
+        <f>SUMIF($B$2:$B$33,$I2,$C$2:$C$33)</f>
+        <v>515</v>
+      </c>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>118</v>
+      </c>
+      <c r="R2" s="26">
+        <f>SUMIFS($C$2:$C$33,$B$2:$B$33,$Q2,$A$2:$A$33,$P2)</f>
+        <v>142</v>
+      </c>
+      <c r="T2" s="42"/>
+      <c r="U2" s="42"/>
+      <c r="V2" s="42"/>
+      <c r="W2" s="40"/>
+      <c r="X2" s="40"/>
+      <c r="Y2" s="40"/>
+      <c r="Z2" s="40"/>
+    </row>
+    <row r="3" spans="1:27" ht="18">
+      <c r="A3" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C3">
+        <v>51</v>
+      </c>
+      <c r="E3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" t="s">
+        <v>117</v>
+      </c>
+      <c r="G3" s="26">
+        <v>81</v>
+      </c>
+      <c r="H3" s="26"/>
+      <c r="I3" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="J3" s="26">
+        <f>SUMIF($B$2:$B$33,$I3,$C$2:$C$33)</f>
+        <v>548</v>
+      </c>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="P3" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>117</v>
+      </c>
+      <c r="R3" s="30">
+        <f>SUMIFS($C$2:$C$33,$B$2:$B$33,$Q3,$A$2:$A$33,$P3)</f>
+        <v>81</v>
+      </c>
+      <c r="T3" s="42"/>
+      <c r="U3" s="42"/>
+      <c r="V3" s="42"/>
+      <c r="W3" s="40"/>
+      <c r="X3" s="40"/>
+      <c r="Y3" s="40"/>
+      <c r="Z3" s="40"/>
+      <c r="AA3" s="9"/>
+    </row>
+    <row r="4" spans="1:27">
+      <c r="A4" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C4">
+        <v>60</v>
+      </c>
+      <c r="E4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G4" s="26">
+        <v>70</v>
+      </c>
+      <c r="H4" s="26"/>
+      <c r="I4" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="J4" s="26">
+        <f>SUMIF($B$2:$B$33,$I4,$C$2:$C$33)</f>
+        <v>592</v>
+      </c>
+      <c r="P4" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>116</v>
+      </c>
+      <c r="R4" s="30">
+        <f>SUMIFS($C$2:$C$33,$B$2:$B$33,$Q4,$A$2:$A$33,$P4)</f>
+        <v>70</v>
+      </c>
+      <c r="T4" s="42"/>
+      <c r="U4" s="42"/>
+      <c r="V4" s="42"/>
+      <c r="W4" s="40"/>
+      <c r="X4" s="40"/>
+      <c r="Y4" s="40"/>
+      <c r="Z4" s="40"/>
+      <c r="AA4" s="10"/>
+    </row>
+    <row r="5" spans="1:27">
+      <c r="A5" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5">
+        <v>41</v>
+      </c>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="J5" s="36">
+        <f>SUM(J2:J4)</f>
+        <v>1655</v>
+      </c>
+      <c r="R5" s="30">
+        <f>SUMIFS($C$2:$C$33,$B$2:$B$33,$Q5,$A$2:$A$33,$P5)</f>
+        <v>0</v>
+      </c>
+      <c r="T5" s="42"/>
+      <c r="U5" s="42"/>
+      <c r="V5" s="42"/>
+      <c r="AA5" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27">
+      <c r="A6" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6">
+        <v>69</v>
+      </c>
+      <c r="E6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" t="s">
+        <v>118</v>
+      </c>
+      <c r="G6" s="26">
+        <v>148</v>
+      </c>
+      <c r="H6" s="26"/>
+      <c r="P6" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>118</v>
+      </c>
+      <c r="R6" s="30">
+        <f>SUMIFS($C$2:$C$33,$B$2:$B$33,$Q6,$A$2:$A$33,$P6)</f>
+        <v>148</v>
+      </c>
+      <c r="AA6" s="12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27">
+      <c r="A7" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7">
+        <v>76</v>
+      </c>
+      <c r="E7" t="s">
+        <v>119</v>
+      </c>
+      <c r="F7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G7" s="26">
+        <v>72</v>
+      </c>
+      <c r="H7" s="26"/>
+      <c r="P7" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>117</v>
+      </c>
+      <c r="R7" s="30">
+        <f>SUMIFS($C$2:$C$33,$B$2:$B$33,$Q7,$A$2:$A$33,$P7)</f>
+        <v>72</v>
+      </c>
+      <c r="AA7" s="12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27">
+      <c r="A8" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8">
+        <v>100</v>
+      </c>
+      <c r="E8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" t="s">
+        <v>116</v>
+      </c>
+      <c r="G8" s="26">
+        <v>194</v>
+      </c>
+      <c r="H8" s="26"/>
+      <c r="P8" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>116</v>
+      </c>
+      <c r="R8" s="30">
+        <f>SUMIFS($C$2:$C$33,$B$2:$B$33,$Q8,$A$2:$A$33,$P8)</f>
+        <v>194</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27">
+      <c r="A9" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9">
+        <v>78</v>
+      </c>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="R9" s="30">
+        <f>SUMIFS($C$2:$C$33,$B$2:$B$33,$Q9,$A$2:$A$33,$P9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27">
+      <c r="A10" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10">
+        <v>56</v>
+      </c>
+      <c r="E10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="26">
+        <v>144</v>
+      </c>
+      <c r="H10" s="26"/>
+      <c r="P10" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>118</v>
+      </c>
+      <c r="R10" s="30">
+        <f>SUMIFS($C$2:$C$33,$B$2:$B$33,$Q10,$A$2:$A$33,$P10)</f>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27">
+      <c r="A11" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G11" s="26">
+        <v>242</v>
+      </c>
+      <c r="H11" s="26"/>
+      <c r="P11" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>117</v>
+      </c>
+      <c r="R11" s="30">
+        <f>SUMIFS($C$2:$C$33,$B$2:$B$33,$Q11,$A$2:$A$33,$P11)</f>
+        <v>242</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27">
+      <c r="A12" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12">
+        <v>22</v>
+      </c>
+      <c r="E12" t="s">
+        <v>120</v>
+      </c>
+      <c r="F12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G12" s="26">
+        <v>193</v>
+      </c>
+      <c r="H12" s="26"/>
+      <c r="P12" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>116</v>
+      </c>
+      <c r="R12" s="30">
+        <f>SUMIFS($C$2:$C$33,$B$2:$B$33,$Q12,$A$2:$A$33,$P12)</f>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27">
+      <c r="A13" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13">
+        <v>60</v>
+      </c>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="R13" s="30">
+        <f>SUMIFS($C$2:$C$33,$B$2:$B$33,$Q13,$A$2:$A$33,$P13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27">
+      <c r="A14" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C14">
+        <v>49</v>
+      </c>
+      <c r="E14" t="s">
+        <v>121</v>
+      </c>
+      <c r="F14" t="s">
+        <v>118</v>
+      </c>
+      <c r="G14" s="26">
+        <v>81</v>
+      </c>
+      <c r="H14" s="26"/>
+      <c r="P14" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>118</v>
+      </c>
+      <c r="R14" s="30">
+        <f>SUMIFS($C$2:$C$33,$B$2:$B$33,$Q14,$A$2:$A$33,$P14)</f>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27">
+      <c r="A15" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C15">
+        <v>30</v>
+      </c>
+      <c r="E15" t="s">
+        <v>121</v>
+      </c>
+      <c r="F15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G15" s="26">
+        <v>153</v>
+      </c>
+      <c r="H15" s="26"/>
+      <c r="P15" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>117</v>
+      </c>
+      <c r="R15" s="30">
+        <f>SUMIFS($C$2:$C$33,$B$2:$B$33,$Q15,$A$2:$A$33,$P15)</f>
+        <v>153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27">
+      <c r="A16" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16">
+        <v>82</v>
+      </c>
+      <c r="E16" t="s">
+        <v>121</v>
+      </c>
+      <c r="F16" t="s">
+        <v>116</v>
+      </c>
+      <c r="G16" s="26">
+        <v>135</v>
+      </c>
+      <c r="H16" s="26"/>
+      <c r="P16" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>116</v>
+      </c>
+      <c r="R16" s="30">
+        <f>SUMIFS($C$2:$C$33,$B$2:$B$33,$Q16,$A$2:$A$33,$P16)</f>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17">
+        <v>31</v>
+      </c>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="R17" s="26"/>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18">
+        <v>23</v>
+      </c>
+      <c r="E18" t="s">
+        <v>122</v>
+      </c>
+      <c r="G18" s="26">
+        <v>1655</v>
+      </c>
+      <c r="H18" s="26"/>
+      <c r="P18" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q18" s="39"/>
+      <c r="R18" s="33">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C21">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C27">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C28">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18">
+      <c r="A30" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C30">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18">
+      <c r="A31" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="C31">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18">
+      <c r="A32" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C33">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="L1:N3"/>
+    <mergeCell ref="T1:V5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>